--- a/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Funções de Data.xlsx
+++ b/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Funções de Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\ALUNOS_FIC\LINELSON.ALUNOS\3 - FUNÇÕES DE TEXTO E DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\3 - FUNÇÕES DE TEXTO E DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A09142-4820-4B79-9B7E-73802F7522BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8B4280-615F-488F-B803-927B70DACDEC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11325" tabRatio="945" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" tabRatio="945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXEMPLO 1" sheetId="1" r:id="rId1"/>
@@ -154,11 +154,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-416]mmmm\-yy;@"/>
     <numFmt numFmtId="166" formatCode="h:mm;@"/>
     <numFmt numFmtId="167" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="172" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -263,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -321,9 +323,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -376,10 +375,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -404,15 +409,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>52917</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>65617</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1000125</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>12056</xdr:rowOff>
+      <xdr:colOff>1053042</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1473</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -440,8 +445,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1600200"/>
-          <a:ext cx="2867025" cy="2412356"/>
+          <a:off x="52917" y="1018117"/>
+          <a:ext cx="2868083" cy="2412356"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -620,15 +625,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>17852</xdr:colOff>
+      <xdr:colOff>52944</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>33588</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1257300</xdr:colOff>
+      <xdr:colOff>1262313</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>130973</xdr:rowOff>
+      <xdr:rowOff>40736</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -656,8 +661,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17852" y="1457325"/>
-          <a:ext cx="2725348" cy="2293148"/>
+          <a:off x="52944" y="1367088"/>
+          <a:ext cx="2728356" cy="2293148"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -733,8 +738,8 @@
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1140994</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>81821</xdr:rowOff>
     </xdr:to>
@@ -944,15 +949,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>171451</xdr:colOff>
+      <xdr:colOff>135732</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>45244</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:colOff>1002506</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>104773</xdr:rowOff>
+      <xdr:rowOff>45242</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -980,8 +985,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="171451" y="1057275"/>
-          <a:ext cx="2781299" cy="2476498"/>
+          <a:off x="135732" y="997744"/>
+          <a:ext cx="2777727" cy="2476498"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1327,49 +1332,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="46"/>
-      <c r="C1" s="42"/>
+      <c r="C1" s="41"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="39"/>
+      <c r="B3" s="9">
+        <f ca="1">TODAY()</f>
+        <v>46099</v>
+      </c>
+      <c r="C3" s="38"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="43"/>
+      <c r="E3" s="42"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="39"/>
+      <c r="B4" s="11">
+        <f ca="1">NOW()</f>
+        <v>46099.909397222225</v>
+      </c>
+      <c r="C4" s="38"/>
       <c r="D4" s="15"/>
-      <c r="E4" s="44"/>
+      <c r="E4" s="43"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="35"/>
+      <c r="B6" s="12">
+        <f ca="1">DAY(B4)</f>
+        <v>18</v>
+      </c>
+      <c r="C6" s="37"/>
+      <c r="D6" s="34"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="12">
+        <f ca="1">MONTH(B4)</f>
+        <v>3</v>
+      </c>
+      <c r="C7" s="37"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="35"/>
+      <c r="B8" s="12">
+        <f ca="1">YEAR(B4)</f>
+        <v>2026</v>
+      </c>
+      <c r="C8" s="37"/>
+      <c r="D8" s="34"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="13"/>
@@ -1379,48 +1399,62 @@
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="39"/>
+      <c r="B10" s="9">
+        <v>38965</v>
+      </c>
+      <c r="C10" s="38"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
+      <c r="B11" s="48">
+        <f ca="1">_xlfn.DAYS(B3,B10)</f>
+        <v>7134</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
+      <c r="B12" s="27">
+        <f ca="1" xml:space="preserve"> (YEAR(B3) - YEAR(B10)) * 12 + MONTH(B3) - MONTH(B10)</f>
+        <v>234</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
+      <c r="B13" s="27">
+        <f ca="1">DATEDIF(B10,B3,"M")</f>
+        <v>234</v>
+      </c>
+      <c r="C13" s="39"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
+      <c r="B14" s="45">
+        <f ca="1">B12/12</f>
+        <v>19.5</v>
+      </c>
+      <c r="C14" s="40"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1486,7 +1520,10 @@
       <c r="B5" s="2">
         <v>43373</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3">
+        <f>NETWORKDAYS(A5,B5,B2)</f>
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="26"/>
@@ -1560,7 +1597,10 @@
       <c r="B5" s="2">
         <v>43404</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3">
+        <f>NETWORKDAYS(A5,B5,B2)</f>
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1629,7 +1669,10 @@
       <c r="B6" s="2">
         <v>43434</v>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3">
+        <f>NETWORKDAYS(A6,B6,B2:B3)</f>
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1704,7 +1747,10 @@
       <c r="B6" s="21">
         <v>43465</v>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="22">
+        <f>NETWORKDAYS(A6,B6,B2:B3)</f>
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1727,77 +1773,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="33">
+      <c r="B2" s="32">
         <v>43101</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="32"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="31"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="29">
         <f ca="1">NOW()</f>
-        <v>45458.665274074076</v>
-      </c>
-      <c r="C4" s="29" t="s">
+        <v>46099.909397222225</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="33">
+      <c r="A5" s="32">
         <v>43101</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="32">
         <v>43131</v>
       </c>
-      <c r="C5" s="31"/>
+      <c r="C5" s="30">
+        <f>NETWORKDAYS(A5,B5,B2)</f>
+        <v>22</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1812,7 +1861,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.42578125" style="6" customWidth="1"/>
     <col min="4" max="4" width="2.7109375" style="6" customWidth="1"/>
     <col min="5" max="5" width="38.5703125" style="6" bestFit="1" customWidth="1"/>
@@ -1881,7 +1930,10 @@
       <c r="B7" s="9">
         <v>43159</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="12">
+        <f>NETWORKDAYS(A7,B7,B2:B4)</f>
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1929,7 +1981,7 @@
       </c>
       <c r="B4" s="24">
         <f ca="1">NOW()</f>
-        <v>45458.665274074076</v>
+        <v>46099.909397222225</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -1942,7 +1994,10 @@
       <c r="B5" s="9">
         <v>43190</v>
       </c>
-      <c r="C5" s="12"/>
+      <c r="C5" s="12">
+        <f>NETWORKDAYS(A5,B5,B2)</f>
+        <v>22</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
@@ -1973,7 +2028,7 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.7109375" style="6" customWidth="1"/>
     <col min="5" max="5" width="38.5703125" style="6" bestFit="1" customWidth="1"/>
@@ -2042,7 +2097,10 @@
       <c r="B7" s="9">
         <v>43220</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="12">
+        <f>NETWORKDAYS(A7,B7,B2:B4)</f>
+        <v>20</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
@@ -2125,7 +2183,10 @@
       <c r="B6" s="2">
         <v>43251</v>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3">
+        <f>NETWORKDAYS(A6,B6,B2:B3)</f>
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="26"/>
@@ -2188,7 +2249,7 @@
       </c>
       <c r="B4" s="24">
         <f ca="1">NOW()</f>
-        <v>45458.665274074076</v>
+        <v>46099.909397222225</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -2201,7 +2262,10 @@
       <c r="B5" s="2">
         <v>43281</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3">
+        <f>NETWORKDAYS(A5,B5,B2)</f>
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="26"/>
@@ -2275,7 +2339,10 @@
       <c r="B5" s="2">
         <v>43312</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3">
+        <f>NETWORKDAYS(A5,B5,B2)</f>
+        <v>22</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="26"/>
@@ -2351,7 +2418,10 @@
       <c r="B5" s="2">
         <v>43343</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3">
+        <f>NETWORKDAYS(A5,B5,B2)</f>
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="26"/>
